--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsOrder.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsOrder.xlsx
@@ -85,22 +85,22 @@
     <t>{.sourceTypeName}</t>
   </si>
   <si>
-    <t>{.remarkde}</t>
-  </si>
-  <si>
-    <t>{.statusNamede}</t>
-  </si>
-  <si>
-    <t>{.labelStatusNamede}</t>
-  </si>
-  <si>
-    <t>{.exceptionReasonde}</t>
-  </si>
-  <si>
-    <t>{.createTimee}</t>
-  </si>
-  <si>
-    <t>{.createUserNamede}</t>
+    <t>{.remark}</t>
+  </si>
+  <si>
+    <t>{.statusName}</t>
+  </si>
+  <si>
+    <t>{.labelStatusName}</t>
+  </si>
+  <si>
+    <t>{.exceptionReason}</t>
+  </si>
+  <si>
+    <t>{.createTime}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
   </si>
 </sst>
 </file>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsOrder.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/logisticsOrder.xlsx
@@ -73,7 +73,7 @@
     <t>{.logisticsChannelName}</t>
   </si>
   <si>
-    <t>{.trackNode}</t>
+    <t>{.trackNo}</t>
   </si>
   <si>
     <t>{.transportNo}</t>
